--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2087,51 +2087,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64964683</v>
+        <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>106329</v>
+        <v>102468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+          <t>vårärt, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455242</v>
+        <v>455179</v>
       </c>
       <c r="R14" t="n">
-        <v>6223030</v>
+        <v>6222939</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,12 +2156,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,42 +2170,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>bokskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tony Svensson, Lennart Söderberg, Sofia Lund, Joachim Krumlinde</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Puggehatten inventeringshelg</t>
-        </is>
-      </c>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64964683</t>
+          <t>https://artportalen.se/Sighting/136640377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6902182</v>
+        <v>64964683</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>106329</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,21 +2205,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221423</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2269,12 +2262,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,7 +2281,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>produktionsbokskog</t>
+          <t>bokskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2299,71 +2292,67 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Tony Svensson, Lennart Söderberg, Sofia Lund, Joachim Krumlinde</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Puggehatten inventeringshelg</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6902182</t>
+          <t>https://artportalen.se/Sighting/64964683</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>81249476</v>
+        <v>6902182</v>
       </c>
       <c r="B16" t="n">
-        <v>91413</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>233194</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Laxfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria flavosalmonicolor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schild, 1990</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Snärjet, bokblandskog, Sk</t>
+          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455283</v>
+        <v>455242</v>
       </c>
       <c r="R16" t="n">
-        <v>6223118</v>
+        <v>6223030</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,17 +2376,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2013-08-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Sporer 7,5-8 x 3,5-4 um, cylindriska-ellipsoida, ibland konstrikta. Med söljor.</t>
+          <t>2013-08-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,17 +2390,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>bokblandskog</t>
+          <t>produktionsbokskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2433,54 +2412,62 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81249476</t>
+          <t>https://artportalen.se/Sighting/6902182</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81249803</v>
+        <v>81249476</v>
       </c>
       <c r="B17" t="n">
-        <v>89823</v>
+        <v>91413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2979</v>
+        <v>233194</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Laxfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Ramaria flavosalmonicolor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Schild, 1990</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tjuvahallarna, vägen, Sk</t>
+          <t>Snärjet, bokblandskog, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455511</v>
+        <v>455283</v>
       </c>
       <c r="R17" t="n">
-        <v>6223040</v>
+        <v>6223118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,19 +2502,28 @@
           <t>2019-09-13</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sporer 7,5-8 x 3,5-4 um, cylindriska-ellipsoida, ibland konstrikta. Med söljor.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>ädellövskog med bok, ek</t>
+          <t>bokblandskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2543,6 +2539,117 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81249476</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>81249803</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89823</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2979</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lömsk flugsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Amanita phalloides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjuvahallarna, vägen, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>455511</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6223040</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>ädellövskog med bok, ek</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81249803</t>
         </is>
@@ -2566,6 +2673,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>136640377</v>
       </c>
       <c r="B14" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
